--- a/assets/translations/Danish.Denmark.da-DK.xlsx
+++ b/assets/translations/Danish.Denmark.da-DK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mspitschan/Projects/LadenburgConsensusStatements/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9F79DD-9599-3543-B514-F902AA7BF458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24710C37-71DC-4955-BDDD-AC8E30B96406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4300" windowWidth="28800" windowHeight="19080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="4300" windowWidth="28800" windowHeight="19080" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="198">
   <si>
     <t>Last name</t>
   </si>
@@ -82,28 +82,53 @@
     <t>Joachim</t>
   </si>
   <si>
+    <t>jsh@ocutune.com</t>
+  </si>
+  <si>
     <t>Ocutune</t>
   </si>
   <si>
-    <t>Chapter</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Statement</t>
-  </si>
-  <si>
-    <t>Simplified statement</t>
-  </si>
-  <si>
-    <t>Contextual information</t>
+    <t>Kapitel</t>
+  </si>
+  <si>
+    <t>Oversættelse</t>
+  </si>
+  <si>
+    <t>Nummer</t>
+  </si>
+  <si>
+    <t>Forklaring</t>
+  </si>
+  <si>
+    <t>Forenklet forklaring</t>
+  </si>
+  <si>
+    <t>Kontekstuel forklaring</t>
   </si>
   <si>
     <t>Light and spectrum (1-6)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lys- og spektrum (1-6) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1A62FF"/>
+        <rFont val="Poppins Bold"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Light can be described by its spectrum: how much energy there is at each wavelength across the visible spectrum (from approximately 380 to 780 nm).</t>
   </si>
   <si>
     <r>
@@ -114,19 +139,53 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Lys- og lysspektrum (1-6) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1A62FF"/>
+      <t>Lys kan beskrives ud fra dets spektrum: hvor meget energi der findes for hver bølgelængde på tværs af det synlige spektrum (fra cirka 380 til 780 nm). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans Bold"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>White light is made up of multiple wavelengths, which we perceive as colours.</t>
+  </si>
+  <si>
+    <t>Hvidt lys består af en mange forskellige bølgelængder, som vi opfatter som farver.  </t>
+  </si>
+  <si>
+    <t>When we see different colours, we are actually seeing different wavelengths of light. Short wavelengths appear violet, while longer wavelengths appear indigo, blue, green, yellow, orange, and red.</t>
+  </si>
+  <si>
+    <r>
+      <t>Når vi ser forskellige farver, svarer det til forskellige bølgelængder i lyset. Lysets korte bølgelængder fremstår som violette, mens lysets længere bølgelængder fremstår som indigo, blå, grøn, gul, orange og rød.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
         <rFont val="Poppins Bold"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Light can be described by its spectrum: how much energy there is at each wavelength across the visible spectrum (from approximately 380 to 780 nm).</t>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>The pattern of one's light exposure across the day and the year can be quite complex, and depends on where one is and what one does.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -137,29 +196,29 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Lys kan beskrives ud fra dets spektrum: hvor meget energi der findes for hver bølgelængde på tværs af det synlige spektrum (fra cirka 380 til 780 nm). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Open Sans Bold"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>White light is made up of multiple wavelengths, which we perceive as colours.</t>
-  </si>
-  <si>
-    <t>Hvidt lys består af en mange forskellige bølgelængder, som vi opfatter som farver.  </t>
-  </si>
-  <si>
-    <t>When we see different colours, we are actually seeing different wavelengths of light. Short wavelengths appear violet, while longer wavelengths appear indigo, blue, green, yellow, orange, and red.</t>
-  </si>
-  <si>
-    <r>
-      <t>Når vi ser forskellige farver, svarer det til forskellige bølgelængder i lyset. Lysets korte bølgelængder fremstår som violette, mens lysets længere bølgelængder fremstår som indigo, blå, grøn, gul, orange og rød.</t>
+      <t>Den lys­eksponering som mennesker udsættes for i løbet af døgnet og året kan være ret komplekst og afhænger af, hvor man befinder sig, og hvad man foretager sig. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>The amount of light around us (or the amount we are exposed to) changes as we move between indoor and outdoor spaces, throughout the day, and across seasons.</t>
+  </si>
+  <si>
+    <t>Mængden af det lys vi udsættes for ændrer sig, når vi bevæger os mellem indendørs og udendørs omgivelser, i løbet af dagen og på tværs af årstiderne.  </t>
+  </si>
+  <si>
+    <t>Light from the sun increases from dawn to midday and decreases in the evening. Depending on location, the amount of light in the day varies greatly between summer and winter.</t>
+  </si>
+  <si>
+    <r>
+      <t>Lyset fra solen tiltager fra daggry til middag og aftager om aftenen. Afhængigt af beliggenheden varierer mængden af dagslys betydeligt mellem sommer og vinter.</t>
     </r>
     <r>
       <rPr>
@@ -182,8 +241,149 @@
     </r>
   </si>
   <si>
-    <t>The pattern of one's light exposure across the day and the year can be quite complex, and depends on where one is and what one does.</t>
+    <t>Light exposure can be described by its intensity: The total amount of energy across all wavelengths from 380 to 780 nm, weighted according to the function of interest.</t>
+  </si>
+  <si>
+    <r>
+      <t>Lys­eksponering kan beskrives ved lysets intensitet; som den samlede mængde energi på tværs af alle bølgelængder fra 380 til 780 nm. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>We can measure light exposure by assessing how intense the light is at different wavelengths.</t>
+  </si>
+  <si>
+    <r>
+      <t>Vi kan måle lys</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FFD13438"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>­</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eksponering ved at vurdere lysets intensitet ved forskellige bølgelængder.  </t>
+    </r>
+  </si>
+  <si>
+    <t>We can characterise a light source by describing how much power it emits at each wavelength. This power is called intensity. Physicists measure intensity, while biological and psychological scientists study how intensity affects various processes.</t>
+  </si>
+  <si>
+    <t>Vi kan karakterisere en lyskilde ved at beskrive, hvor meget effekt den udsender ved hver bølgelængde. Denne effekt kaldes intensitet. Fysikere måler intensitet, mens forskere i biologi og fysiologi undersøger, hvordan intensitet påvirker forskellige processer.</t>
+  </si>
+  <si>
+    <t>Daylight has what we call a broad spectrum, with a lot of energy across many wavelengths.</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Dagslys har det et bredt spektrum, med meget energi fordelt på mange bølgelængder. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Daylight has a wide range of energy across multiple wavelengths – it can be separated into all the colours of the rainbow.</t>
+  </si>
+  <si>
+    <t>Dagslys har et bredt spektrum af energi på tværs af mange bølgelængder der kan opdeles i alle regnbuens farver.  </t>
+  </si>
+  <si>
+    <t>Daylight, a combination of direct sunlight and scattered sky light, contains all visible wavelengths and more. Changes in the time of day and weather conditions shift the wavelength composition. This shift changes the colour that daylight appears.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dagslys som er en kombinationen af direkte sollys og diffust himmellys, indeholder alle synlige bølgelængder og mere til. Tidspunktet på dagen og vejrforholdene ændrer bølgelængdesammensætningen. Denne forskydning ændrer derfor også den farvesammensætning, som dagslyset fremstår med.  </t>
+  </si>
+  <si>
+    <t>Different electric light sources (e.g., LED or fluorescent lamps, etc.) have different spectra.</t>
+  </si>
+  <si>
+    <r>
+      <t>Forskellige lyskilder (f.eks. LED- eller lysstofrør) har forskellige lysspektre. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Different light sources generate light in different ways, producing distinct wavelengths or colour.</t>
+  </si>
+  <si>
+    <t>Forskellige lyskilder frembringer lys på forskellige måder og producerer særskilte lysspektre med forskellige farvesammensætninger.  </t>
+  </si>
+  <si>
+    <t>Different light source technologies use various materials to convert electricity into light. Different materials cause the intensity of light to spread across different wavelengths in different ways. This spread of light across wavelengths is known as spectral distribution.</t>
+  </si>
+  <si>
+    <t>Forskellige lysteknologier anvender forskellige materialer til at omdanne elektricitet til lys. Forskellige materialer får lysintensiteten til at fordele sig forskelligt over spektrets forskellige bølgelængder. Denne fordeling af lys på tværs af bølgelængder kaldes spektralfordeling.  </t>
+  </si>
+  <si>
+    <t>The properties of daylight (spectrum, intensity and spatial distribution) vary throughout the day and the year, and with changing weather.</t>
+  </si>
+  <si>
+    <r>
+      <t>Dagslysets egenskaber (spektrum og intensitet) varierer i løbet af dagen og året samt med skiftende vejrforhold. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>The colour, intensity, and pattern of daylight change throughout the day, with seasons, and weather.</t>
+  </si>
+  <si>
+    <t>Dagslysets farve, intensitet og mønster ændrer sig i løbet af dagen samt med årstiderne og vejrforholdene.  </t>
+  </si>
+  <si>
+    <t>As sunlight travels through the atmosphere, blue light is scattered more than other wavelengths. This makes the sky appear blue.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Når sollyset bevæger sig gennem atmosfæren, spredes blåt, kortbølget lys mere end andre synlige bølgelængder. Det er grunden til at himlen ser blå ud.  </t>
+  </si>
+  <si>
+    <t>Human photoreceptors (7-9)</t>
   </si>
   <si>
     <r>
@@ -194,33 +394,150 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Den lys­eksponering som mennesker udsættes for i løbet af døgnet og året kan være ret komplekst og afhænger af, hvor man befinder sig, og hvad man foretager sig. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
+      <t>Menneskets fotoreceptorer (7-9) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1A62FF"/>
         <rFont val="Poppins Bold"/>
       </rPr>
       <t> </t>
     </r>
   </si>
   <si>
-    <t>The amount of light around us (or the amount we are exposed to) changes as we move between indoor and outdoor spaces, throughout the day, and across seasons.</t>
-  </si>
-  <si>
-    <t>Mængden af det lys vi udsættes for ændrer sig, når vi bevæger os mellem indendørs og udendørs omgivelser, i løbet af dagen og på tværs af årstiderne.  </t>
-  </si>
-  <si>
-    <t>Light from the sun increases from dawn to midday and decreases in the evening. Depending on location, the amount of light in the day varies greatly between summer and winter.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lyset fra solen tiltager fra daggry til middag og aftager om aftenen. Afhængigt af beliggenheden varierer mængden af dagslys betydeligt mellem sommer og vinter.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+    <t>The human eye contains the retina, which has several photosensitive cells that differ in their responses to different wavelengths.</t>
+  </si>
+  <si>
+    <t>Nethinden i menneskets øje, indeholder en række fotoreceptorer som er lysfølsomme celler. Disse fotoreceptorer adskiller sig fra hinanden ved deres respons på forskellige bølgelængder.  </t>
+  </si>
+  <si>
+    <t>In the eye, the retina contains cells that allow us to detect different colours.</t>
+  </si>
+  <si>
+    <t>I øjets nethinde findes forskellige fotoreceptorer, der gør det muligt for os at se og opfatte forskellige farver.  </t>
+  </si>
+  <si>
+    <r>
+      <t>In the human eye, the retina contains light-sensitive cells that convert light into signals for the brain. These cells are called cones, rods, and intrinsically photosensitive retinal ganglion cells (ipRGCs)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color rgb="FF242424"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>26,27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF242424"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>I det menneskelige øjes nethinde, findes lysfølsomme celler eller fotoreceptorer, der omdanner lys til signaler til hjernen. Disse celler kaldes tappe, stave og intrinsisk lysfølsomme retinale ganglieceller (ipRGC'er).  </t>
+  </si>
+  <si>
+    <t>The cones allow us to see colour, motion and spatial detail in bright lighting conditions.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tappe hjælper os med at se farver, bevægelse og genstande under øgede lysforhold.  </t>
+  </si>
+  <si>
+    <t>Cone cells help us see colours, movement, and objects in bright light.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cones are specialized cells in the retina. They are named for their shape (how they appear under a microscope). The highest density of cones is in the fovea (in the centre of the retina).</t>
+  </si>
+  <si>
+    <t>Tappe er specialiserede celler i nethinden. De har fået deres navn efter deres form (som de ser ud under et mikroskop). Den højeste tæthed af tappe findes i fovea (i midten af nethinden).  </t>
+  </si>
+  <si>
+    <t>The rods allow us to see rudimentary spatial detail under dim light.</t>
+  </si>
+  <si>
+    <t>Stavene hjælper os med at se former og detaljer i svagt lys.  </t>
+  </si>
+  <si>
+    <t>Rod cells help us see shapes and details in dim light.</t>
+  </si>
+  <si>
+    <t>Rods are highly sensitive to low light levels. They are essential for seeing at night.</t>
+  </si>
+  <si>
+    <t>Stavene er meget følsomme over for svage belysningsniveauer. De er derfor afgørende for at kunne se og orientere sig om natten.  </t>
+  </si>
+  <si>
+    <t>Non-visual effects of light (10-20)</t>
+  </si>
+  <si>
+    <t>Lysets ikke-billeddannende påvirkning (10-20)</t>
+  </si>
+  <si>
+    <t>The intrinsically photosensitive retinal ganglion cells (ipRGCs) convert light into signals that influence many physiological functions.</t>
+  </si>
+  <si>
+    <r>
+      <t>De intrinsisk-lysfølsomme retinale ganglieceller (ipRGC'er) omdanner lys til signaler, der påvirker en lang række fysiologiske funktioner. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>When ipRGCs detect light, they send signals to the brain to regulate various bodily functions.</t>
+  </si>
+  <si>
+    <t>Når ipRGC'er registrerer lys, sender de signaler til hjernen, som derigennem regulerer en række forskellige kropsfunktioner.  </t>
+  </si>
+  <si>
+    <t>ipRGCs send electrical signals to brain regions that regulate sleep-wake cycles, alertness, and mood.</t>
+  </si>
+  <si>
+    <t>ipRGC'er sender elektriske signaler til hjerneområder, der regulerer søvn-vågen-cyklusser, vagtsomhed og humør.  </t>
+  </si>
+  <si>
+    <t>Predominantly through the ipRGCs, light causes the suppression of melatonin in the evening and at night.</t>
+  </si>
+  <si>
+    <t>Gennem ipRGC'erne forårsager lys en undertrykkelse af melatonin.</t>
+  </si>
+  <si>
+    <t>Light blocks the production of melatonin (a hormone that regulates sleep-wake cycles), particularly in the evening and at night.</t>
+  </si>
+  <si>
+    <t>Lys blokerer for produktionen af ‘mørkehormonet’ melatonin (et hormon, der regulerer søvn-vågen-cyklusser), især om aftenen og om natten.  </t>
+  </si>
+  <si>
+    <t>ipRGCs express melanopsin (a light-sensitive protein). When ipRGCs detect bright light, melanopsin becomes activated. This activation triggers a neuronal pathway, blocking the production of melatonin in the pineal gland.</t>
+  </si>
+  <si>
+    <t>ipRGC'er besidder et lysfølsomt protein som kaldes melanopsin. Når cellerne udsættes for kraftigt lys, aktiveres melanopsin, hvilket får ipRGC'erne til at sende signaler til hjernen. Disse signaler aktiverer et neurologisk kredsløb, der reducerer dannelse af melatonin i koglekirtlen.  </t>
+  </si>
+  <si>
+    <t>Light is the main signal that ensures the circadian system is synchronized to the 24- hour cycles in the environment.</t>
+  </si>
+  <si>
+    <r>
+      <t>Lys er den vigtigste påvirkning af mennesker, der sikrer, at døgnrytmesystemet forbliver synkroniseret til døgnets og omgivelsernes 24-timers cyklusser. </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color rgb="FF343A40"/>
         <rFont val="Poppins Bold"/>
@@ -228,9 +545,30 @@
       </rPr>
       <t> </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+  </si>
+  <si>
+    <t>Light is the primary signal that synchronizes the body's internal clock with the sun’s day-night cycle.</t>
+  </si>
+  <si>
+    <t>Lys er det primære signal, der synkroniserer kroppens indre ur.  </t>
+  </si>
+  <si>
+    <t>Light helps regulate the body's internal rhythms. This ensures biological processes start and stop at appropriate times.</t>
+  </si>
+  <si>
+    <t>Lys hjælper med at regulere kroppens iboende rytmer. Det rigtige lys på de rigtige tidspunkter at dagen kan sikre, at biologiske processer starter og stopper på passende tidspunkter som er optimal for vores sundhed.  </t>
+  </si>
+  <si>
+    <t>Light directly influences the biological clock in the brain, regulating sleep-wake cycles and other daily physiological rhythms.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Lys påvirker det biologiske ur i hjernen direkte og regulerer samtidig søvn-vågen-cyklusser samt andre fysiologiske funktioner der udviser en døgnrytme. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
         <color rgb="FF343A40"/>
         <rFont val="Poppins Bold"/>
         <charset val="1"/>
@@ -239,11 +577,52 @@
     </r>
   </si>
   <si>
-    <t>Light exposure can be described by its intensity: The total amount of energy across all wavelengths from 380 to 780 nm, weighted according to the function of interest.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lys­eksponering kan beskrives ved lysets intensitet; som den samlede mængde energi på tværs af alle bølgelængder fra 380 til 780 nm. </t>
+    <t xml:space="preserve">Light influences the body’s internal clock, which regulates sleep-wake patterns and other daily rhythms. </t>
+  </si>
+  <si>
+    <t>Lys påvirker kroppens indre ur, som regulerer søvn- og vågenmønstre, samt andre fysiologiske funktioner der udviser en døgnrytme"  </t>
+  </si>
+  <si>
+    <t>Light exposure influences sleep, hormone release, metabolism, and alertness.</t>
+  </si>
+  <si>
+    <t>Lys­eksponering påvirker søvn, hormonudskillelse, stofskifte og vågenhed.    </t>
+  </si>
+  <si>
+    <t>Light in the morning can advance the circadian clock, and light in the evening can delay the circadian clock.</t>
+  </si>
+  <si>
+    <r>
+      <t>Lys om morgenen kan faseskifte dit indre ur mod tidligere (Phase-Advance), og lys om aftenen kan forsinke dit indre ur mod senere (Phase-delay). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Semi-Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Morning light promotes earlier bedtime and wake time, while evening light can delay bedtime and waking.</t>
+  </si>
+  <si>
+    <t>At få lys om morgenen hjælper dig med at falde i søvn og vågne tidligere, imens lys om aftenen kan skubbe din sengetid og opvågning til senere.  </t>
+  </si>
+  <si>
+    <t>Light tells the brain to become active. Light in the morning advances the body’s internal clock (shifts it to an earlier “time”), while light in the evening delays it (shifts it to a later “time”).</t>
+  </si>
+  <si>
+    <t>Lys signalerer til hjernen, at den skal blive og forblive aktiv. Lys om morgenen fremrykker kroppens indre ur (skubber det til et tidligere ‘tidspunkt’), mens lys om aftenen forsinker det (skubber det til et senere ‘tidspunkt’). </t>
+  </si>
+  <si>
+    <t>Light can also boost alertness and cognitive function under some conditions.</t>
+  </si>
+  <si>
+    <r>
+      <t>Lys kan også under visse betingelser øge vågenhed og kognitive funktioner.  </t>
     </r>
     <r>
       <rPr>
@@ -256,23 +635,19 @@
     </r>
   </si>
   <si>
-    <t>We can measure light exposure by assessing how intense the light is at different wavelengths.</t>
-  </si>
-  <si>
-    <r>
-      <t>Vi kan måle lys</t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="12"/>
-        <color rgb="FFD13438"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>­</t>
-    </r>
+    <t>In certain situations, light can improve alertness and ability to think.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Under visse omstændigheder kan høje belysningsstyrker øge årvågenhed/ vågenhed og forbedre kognition både i dagtimerne og om natten.  </t>
+  </si>
+  <si>
+    <t>Under some conditions, exposure to high-intensity light during the day and night enhances alertness and improves cognitive performance.</t>
+  </si>
+  <si>
+    <t>What determines these physiological responses to light is primarily determined by how much light reaches the retina and stimulates the ipRGCs at a certain time.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -281,22 +656,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>eksponering ved at vurdere lysets intensitet ved forskellige bølgelængder.  </t>
-    </r>
-  </si>
-  <si>
-    <t>We can characterise a light source by describing how much power it emits at each wavelength. This power is called intensity. Physicists measure intensity, while biological and psychological scientists study how intensity affects various processes.</t>
-  </si>
-  <si>
-    <t>Vi kan karakterisere en lyskilde ved at beskrive, hvor meget effekt den udsender ved hver bølgelængde. Denne effekt kaldes intensitet. Fysikere måler intensitet, mens biologiske og psykologiske forskere undersøger, hvordan intensitet påvirker forskellige processer.</t>
-  </si>
-  <si>
-    <t>Daylight has what we call a broad spectrum, with a lot of energy across many wavelengths.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Dagslys har det et bredt spektrum, med meget energi fordelt på mange bølgelængder. </t>
+      <t>Disse fysiologiske funktioner drevet af lys bestemmes primært af, på et givent tidspunkt, hvor meget lys der når frem til nethinden, og hvor meget de stimulerer de intrinsisk-lysfølsomme retinale ganglieceller (ipRGC’er).  </t>
+    </r>
+  </si>
+  <si>
+    <t>The body's response to light depends on how much light and what time the light reaches the ipRGCs in the retina.</t>
+  </si>
+  <si>
+    <t>Kroppens reaktion på lys afhænger af, hvor meget lys der når ipRGC’erne i øjets nethinde, og på hvilket tidspunkt det sker.  </t>
+  </si>
+  <si>
+    <t>The response of ipRGCs likely depends on the time of day and circadian factors.</t>
+  </si>
+  <si>
+    <t>Higher light levels in the evening can increase the time to fall asleep.</t>
+  </si>
+  <si>
+    <r>
+      <t>Højere belysningslysniveauer om aftenen kan forlænge den tid, det tager at falde i søvn. </t>
     </r>
     <r>
       <rPr>
@@ -309,24 +686,24 @@
     </r>
   </si>
   <si>
-    <t>Daylight has a wide range of energy across multiple wavelengths – it can be separated into all the colours of the rainbow.</t>
-  </si>
-  <si>
-    <t>Dagslys har et bredt spektrum af energi på tværs af mange bølgelængder der kan opdeles i alle regnbuens farver.  </t>
-  </si>
-  <si>
-    <t>Daylight, a combination of direct sunlight and scattered sky light, contains all visible wavelengths and more. Changes in the time of day and weather conditions shift the wavelength composition. This shift changes the colour that daylight appears.</t>
+    <t>Evening light exposure can make it harder to fall asleep.</t>
+  </si>
+  <si>
+    <t>Udsættes man for lys om aftenen, kan det være sværere at falde i søvn.  </t>
+  </si>
+  <si>
+    <t>Evening light exposure tells the body it is still daytime. This increases alertness and shifts the internal clock to a later time.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Dagslys som er en kombinationen af direkte sollys og diffust himmellys, indeholder alle synlige bølgelængder og mere til. Tidspunktet på dagen og vejrforholdene ændrer bølgelængdesammensætningen. Denne forskydning ændrer derfor også den farvesammensætning, som dagslyset fremstår med.  </t>
-  </si>
-  <si>
-    <t>Different electric light sources (e.g., LED or fluorescent lamps, etc.) have different spectra.</t>
-  </si>
-  <si>
-    <r>
-      <t>Forskellige lyskilder (f.eks. LED- eller lysstofrør) har forskellige lysspektre. </t>
+    <t>Lys om aftenen fortæller kroppen, at det stadig er dag. Herved øges vågenhed, samt forskydning af det indre ur til et senere ‘tidspunkt’.  </t>
+  </si>
+  <si>
+    <t>Higher light levels during the daytime can improve mood.</t>
+  </si>
+  <si>
+    <r>
+      <t>Højere belysningsniveauer i dagtimerne kan forbedre humøret. </t>
     </r>
     <r>
       <rPr>
@@ -339,23 +716,23 @@
     </r>
   </si>
   <si>
-    <t>Different light sources generate light in different ways, producing distinct wavelengths or colour.</t>
-  </si>
-  <si>
-    <t>Forskellige lyskilder frembringer lys på forskellige måder og producerer særskilte lysspektre med forskellige farvesammensætninger.  </t>
-  </si>
-  <si>
-    <t>Different light source technologies use various materials to convert electricity into light. Different materials cause the intensity of light to spread across different wavelengths in different ways. This spread of light across wavelengths is known as spectral distribution.</t>
-  </si>
-  <si>
-    <t>Forskellige lysteknologier anvender forskellige materialer til at omdanne elektricitet til lys. Forskellige materialer får lysintensiteten til at fordele sig forskelligt over spektrets forskellige bølgelængder. Denne fordeling af lys på tværs af bølgelængder kaldes spektralfordeling.  </t>
-  </si>
-  <si>
-    <t>The properties of daylight (spectrum, intensity and spatial distribution) vary throughout the day and the year, and with changing weather.</t>
-  </si>
-  <si>
-    <r>
-      <t>Dagslysets egenskaber (spektrum og intensitet) varierer i løbet af dagen og året samt med skiftende vejrforhold. </t>
+    <t>Bright light during the day can improve mood.</t>
+  </si>
+  <si>
+    <t>En højere belysningsstyrke i dagtimerne kan forbedre humøret.  </t>
+  </si>
+  <si>
+    <t>Exposure to natural daylight (the sun) or high-intensity electric light, when free from glare, can reduce stress and improve emotional balance.</t>
+  </si>
+  <si>
+    <t>Eksponering for naturligt dagslys (solen) eller elektrisk belysning med høj intensitet kan, når det er blændfrit, medvirke til at reducere stress og forbedre den ‘følelsesmæssige balance’.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higher light levels during the daytime can improve sleep quality in the following night. </t>
+  </si>
+  <si>
+    <r>
+      <t>Højere belysningsniveauer i dagtimerne kan forbedre søvnkvaliteten den efterfølgende nat. </t>
     </r>
     <r>
       <rPr>
@@ -368,20 +745,197 @@
     </r>
   </si>
   <si>
-    <t>The colour, intensity, and pattern of daylight change throughout the day, with seasons, and weather.</t>
-  </si>
-  <si>
-    <t>Dagslysets farve, intensitet og mønster ændrer sig i løbet af dagen samt med årstiderne og vejrforholdene.  </t>
-  </si>
-  <si>
-    <t>As sunlight travels through the atmosphere, blue light is scattered more than other wavelengths. This makes the sky appear blue.</t>
+    <t>Exposure to more intense light during the day can improve sleep.</t>
+  </si>
+  <si>
+    <t>Udsættelse for intenst lys i dagtimerne kan forbedre søvn.  </t>
+  </si>
+  <si>
+    <t>Exposure to higher daytime light levels reduces sleep fragmentation (awakening throughout the night) and increases deep sleep at night.</t>
+  </si>
+  <si>
+    <t>Udsættelse for højere belysningsniveauer i dagtimerne reducerer søvnfragmentering (opvågninger i løbet af natten) og øger mængden af dyb søvn om natten.  </t>
+  </si>
+  <si>
+    <t>Following a medically-prescribed protocol for bright light, exposure in the morning can lead to improvements in mood for people with certain clinical diagnoses.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>Når sollyset bevæger sig gennem atmosfæren, spredes blåt, kortbølget lys mere end andre synlige bølgelængder. Det er grunden til at himlen ser blå ud.  </t>
-  </si>
-  <si>
-    <t>Human photoreceptors (7-9)</t>
+    <r>
+      <t>Ved at følge en medicinsk-/ Lægeordineret protokol for lysterapi kan lyseksponering om morgenen føre til forbedringer i humør hos personer med visse kliniske diagnoser. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Semi-Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Doctors may prescribe light therapy as treatment for winter depression and other health conditions.</t>
+  </si>
+  <si>
+    <t>Læger kan vælge at ordinere lysterapi som behandling for vinterdepression og andre helbredstilstande.  </t>
+  </si>
+  <si>
+    <t>Exposure to bright light has been shown to improve depressive symptoms in individuals with Seasonal Affective Disorder.</t>
+  </si>
+  <si>
+    <t>Eksponering for øgede belysningsstyrker gennem lysterapi har vist sig at forbedre depressive symptomer hos personer med vinterdepression (Seasonal Affective Disorder).  </t>
+  </si>
+  <si>
+    <t>Influencing factors to the non-visual effects of light (21-23)</t>
+  </si>
+  <si>
+    <r>
+      <t>Faktorer med indvirkning på lysets ikke-billeddannede påvirkninger (21–23). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1A62FF"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>A healthy pattern of daily light exposure includes a rhythm of bright light and darkness every day.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>En sund rutine for daglig lyseksponering, skaber en rytme, der både indeholder perioder med øgede belysningsstyrker og perioder med mørke henover døgnet. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>A healthy daily routine includes bright light during the day and darkness at night.</t>
+  </si>
+  <si>
+    <t>En sund daglig rutine indebærer øgede belysningsstyrker i dagtimerne og mørke om natten.  </t>
+  </si>
+  <si>
+    <t>Maintaining a regular pattern of bright light during the day and darkness at night is associated with better physical and mental health.</t>
+  </si>
+  <si>
+    <t>At opretholde et regelmæssigt mønster med øgede belysningsstyrker i dagtimerne og mørke om natten er forbundet med bedre fysisk og mental sundhed.  </t>
+  </si>
+  <si>
+    <t>Age can influence the physiological effect of light on humans, as less light reaches the retina because of ageing.</t>
+  </si>
+  <si>
+    <r>
+      <t>Alder kan påvirke lysets fysiologiske effekt på mennesker, da mindre lys med alderen når øjets nethinde. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>As people age, the lenses of the eye can become less transparent, which may reduce the effects of light on the internal clock and sleep.</t>
+  </si>
+  <si>
+    <t>Med alderen kan øjets linser blive mindre gennemsigtig og klar. Dette kan nedsætte lysets understøttende virkning på det indre ur og søvnen.  </t>
+  </si>
+  <si>
+    <t>With age, the eye’s lenses become less transparent, which may reduce the body’s response to light exposure.</t>
+  </si>
+  <si>
+    <t>Med alderen bliver øjets linse mindre transparent, hvilket kan reducere kroppens respons på en given lyseksponering.  </t>
+  </si>
+  <si>
+    <t>There are substantial individual differences in the physiological response to light.</t>
+  </si>
+  <si>
+    <r>
+      <t>Der findes betydelige individuelle forskelle i hvordan lyset påvirker os.   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>How people respond to light can vary greatly.</t>
+  </si>
+  <si>
+    <t>Hvordan mennesker påvirkes af lys kan variere meget.  </t>
+  </si>
+  <si>
+    <t>Individual differences in light sensitivity are influenced by factors such as age, genetics, and behavior.</t>
+  </si>
+  <si>
+    <t>De Individuelle forskelle i lysfølsomhed influeres af faktorer som alder, genetik og adfærd.  </t>
+  </si>
+  <si>
+    <t>Research in the non-visual effects of light (24-26)</t>
+  </si>
+  <si>
+    <r>
+      <t>Forskning i lysets ikke-billeddannende påvirkninger (24–26). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1A62FF"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>The majority of studies on the physiological effects of light have been performed in the laboratory.</t>
+  </si>
+  <si>
+    <r>
+      <t>Størstedelen af de studier som har set på lysets fysiologiske påvirkning er blevet udført i laboratorier. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Most research on light’s effects on the body has been conducted in the laboratory.</t>
+  </si>
+  <si>
+    <t>Størstedelen af forskningen i lysets indvirkning på kroppen er udført i laboratorier.  </t>
+  </si>
+  <si>
+    <t>Studies investigating light exposure in the real-world are needed.</t>
+  </si>
+  <si>
+    <t>Der er derfor behov for flere studier, der undersøger lyseksponering i virkelige omgivelser i den virkelige verden.  </t>
   </si>
   <si>
     <r>
@@ -392,7 +946,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Menneskets fotoreceptorer (7-9) </t>
+      <t>Forskning i lysets ikke-billeddannende påvirkninger (24–26). </t>
     </r>
     <r>
       <rPr>
@@ -404,135 +958,29 @@
     </r>
   </si>
   <si>
-    <t>The human eye contains the retina, which has several photosensitive cells that differ in their responses to different wavelengths.</t>
-  </si>
-  <si>
-    <t>Nethinden i menneskets øje, indeholder en række fotoreceptorer som er lysfølsomme celler. Disse fotoreceptorer adskiller sig fra hinanden ved deres respons på forskellige bølgelængder.  </t>
-  </si>
-  <si>
-    <t>In the eye, the retina contains cells that allow us to detect different colours.</t>
-  </si>
-  <si>
-    <t>I øjets nethinde findes forskellige fotoreceptorer, der gør det muligt for os at se og opfatte forskellige farver.  </t>
-  </si>
-  <si>
-    <r>
-      <t>In the human eye, the retina contains light-sensitive cells that convert light into signals for the brain. These cells are called cones, rods, and intrinsically photosensitive retinal ganglion cells (ipRGCs)</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF242424"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>26,27</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF242424"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>I det menneskelige øjes nethinde, findes lysfølsomme celler eller fotoreceptorer, der omdanner lys til signaler til hjernen. Disse celler kaldes tappe, stave og intrinsisk lysfølsomme retinale ganglieceller (ipRGC'er).  </t>
-  </si>
-  <si>
-    <t>The cones allow us to see colour, motion and spatial detail in bright lighting conditions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tappe hjælper os med at se farver, bevægelse og genstande under øgede lysforhold.  </t>
-  </si>
-  <si>
-    <t>Cone cells help us see colours, movement, and objects in bright light.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cones are specialized cells in the retina. They are named for their shape (how they appear under a microscope). The highest density of cones is in the fovea (in the centre of the retina).</t>
-  </si>
-  <si>
-    <t>Tappe er specialiserede celler i nethinden. De har fået deres navn efter deres form (som den ser ud under et mikroskop). Den højeste tæthed af tappe findes i fovea (i midten af nethinden).  </t>
-  </si>
-  <si>
-    <t>The rods allow us to see rudimentary spatial detail under dim light.</t>
-  </si>
-  <si>
-    <t>Stavene hjælper os med at se former og detaljer i svagt lys.  </t>
-  </si>
-  <si>
-    <t>Rod cells help us see shapes and details in dim light.</t>
-  </si>
-  <si>
-    <t>Rods are highly sensitive to low light levels. They are essential for seeing at night.</t>
-  </si>
-  <si>
-    <t>Stavene er meget følsomme over for svage belysningsniveauer. De er derfor afgørende for at kunne se og orientere sig om natten.  </t>
-  </si>
-  <si>
-    <t>Non-visual effects of light (10-20)</t>
-  </si>
-  <si>
-    <t>Lysets ikke-billeddannende påvirkning (10-20)</t>
-  </si>
-  <si>
-    <t>The intrinsically photosensitive retinal ganglion cells (ipRGCs) convert light into signals that influence many physiological functions.</t>
-  </si>
-  <si>
-    <r>
-      <t>De intrinsisk-lysfølsomme retinale ganglieceller (ipRGC'er) omdanner lys til signaler, der påvirker en lang række fysiologiske funktioner. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>When ipRGCs detect light, they send signals to the brain to regulate various bodily functions.</t>
-  </si>
-  <si>
-    <t>Når ipRGC'er registrerer lys, sender de signaler til hjernen, som derigennem regulerer en række forskellige kropsfunktioner.  </t>
-  </si>
-  <si>
-    <t>ipRGCs send electrical signals to brain regions that regulate sleep-wake cycles, alertness, and mood.</t>
-  </si>
-  <si>
-    <t>ipRGC'er sender elektriske signaler til hjerneområder, der regulerer søvn-vågen-cyklusser, vagtsomhed og humør.  </t>
-  </si>
-  <si>
-    <t>Predominantly through the ipRGCs, light causes the suppression of melatonin in the evening and at night.</t>
-  </si>
-  <si>
-    <t>Gennem ipRGC'erne forårsager lys en undertrykkelse af melatonin.</t>
-  </si>
-  <si>
-    <t>Light blocks the production of melatonin (a hormone that regulates sleep-wake cycles), particularly in the evening and at night.</t>
-  </si>
-  <si>
-    <t>Lys blokerer for produktionen af ‘mørkehormonet’ melatonin (et hormon, der regulerer søvn-vågen-cyklusser), især om aftenen og om natten.  </t>
-  </si>
-  <si>
-    <t>ipRGCs express melanopsin (a light-sensitive protein). When ipRGCs detect bright light, melanopsin becomes activated. This activation triggers a neuronal pathway, blocking the production of melatonin in the pineal gland.</t>
-  </si>
-  <si>
-    <t>ipRGC'er besidder et lysfølsomt protein som kaldes melanopsin. Når cellerne udsættes for kraftigt lys, aktiveres melanopsin, hvilket får ipRGC'erne til at sende signaler til hjernen. Disse signaler aktiverer et neurologisk kredsløb, der reducerer dannelse af melatonin i koglekirtlen.  </t>
-  </si>
-  <si>
-    <t>Light is the main signal that ensures the circadian system is synchronized to the 24- hour cycles in the environment.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lys er den vigtigste påvirkning af mennesker, der sikrer, at døgnrytmesystemet forbliver synkroniseret til døgnets og omgivelsernes 24-timers cyklusser. </t>
+    <t>There is a need for studies on the physiological effects of light incorporating a broad range of study populations.</t>
+  </si>
+  <si>
+    <t>Der er behov for studier af lysets fysiologiske påvirkninger, som inddrager et bredere udvalg af studiepopulationer.  </t>
+  </si>
+  <si>
+    <t>More studies are needed to understand how light influences health in different groups of people.</t>
+  </si>
+  <si>
+    <t>Der er behov for flere studier for at få en bedre forståelse af, hvordan lys påvirker sundheden i forskellige populationer.  </t>
+  </si>
+  <si>
+    <t>Most studies on the physiological effects of light have focused on limited populations (specific age groups, ethnicities, or health conditions). It is important that future research studies more diverse populations over wider geographical regions.</t>
+  </si>
+  <si>
+    <t>De fleste studier af lysets fysiologiske påvirkninger har fokuseret på begrænsede populationer (bestemte aldersgrupper, etniciteter eller helbredstilstande). Det er derfor vigtigt, at fremtidig forskning i større grad søger at undersøge mere mangfoldige populationer på tværs af bredere geografiske områder.  </t>
+  </si>
+  <si>
+    <t>The physiological effects of light are an area of active investigation.</t>
+  </si>
+  <si>
+    <r>
+      <t>Lysets fysiologiske påvirkning er et forskningsområde under aktiv udforskning og udvikling. </t>
     </r>
     <r>
       <rPr>
@@ -545,395 +993,16 @@
     </r>
   </si>
   <si>
-    <t>Light is the primary signal that synchronizes the body's internal clock with the sun’s day-night cycle.</t>
-  </si>
-  <si>
-    <t>Lys er det primære signal, der synkroniserer kroppens indre ur.  </t>
-  </si>
-  <si>
-    <t>Light helps regulate the body's internal rhythms. This ensures biological processes start and stop at appropriate times.</t>
-  </si>
-  <si>
-    <t>Lys hjælper med at regulere kroppens iboende rytmer. Det rigtige lys på de rigtige tidspunkter at dagen kan sikre, at biologiske processer starter og stopper på passende tidspunkter som er optimal for vores sundhed.  </t>
-  </si>
-  <si>
-    <t>Light directly influences the biological clock in the brain, regulating sleep-wake cycles and other daily physiological rhythms.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Lys påvirker det biologiske ur i hjernen direkte og regulerer samtidig søvn-vågen-cyklusser samt andre fysiologiske funktioner der udviser en døgnrytme. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Light influences the body’s internal clock, which regulates sleep-wake patterns and other daily rhythms. </t>
-  </si>
-  <si>
-    <t>Lys påvirker kroppens indre ur, som regulerer søvn- og vågenmønstre, samt andre fysiologiske funktioner der udviser en døgnrytme"  </t>
-  </si>
-  <si>
-    <t>Light exposure influences sleep, hormone release, metabolism, and alertness.</t>
-  </si>
-  <si>
-    <t>Lys­eksponering påvirker søvn, hormonudskillelse, stofskifte og vågenhed.    </t>
-  </si>
-  <si>
-    <t>Light in the morning can advance the circadian clock, and light in the evening can delay the circadian clock.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lys om morgenen kan faseskifte dit indre ur mod tidligere (Phase-Advance), og lys om aftenen kan forsinke dit indre ur mod senere (Phase-delay). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Semi-Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Morning light promotes earlier bedtime and wake time, while evening light can delay bedtime and waking.</t>
-  </si>
-  <si>
-    <t>At få lys om morgenen hjælper dig med at falde i søvn og vågne tidligere, imens lys om aftenen kan skubbe din sengetid og opvågning til senere.  </t>
-  </si>
-  <si>
-    <t>Light tells the brain to become active. Light in the morning advances the body’s internal clock (shifts it to an earlier “time”), while light in the evening delays it (shifts it to a later “time”).</t>
-  </si>
-  <si>
-    <t>Lys signalerer til hjernen, at den skal blive og forblive aktiv. Lys om morgenen fremrykker kroppens indre ur (skubber det til et tidligere ‘tidspunkt’), mens lys om aftenen forsinker det (skubber det til et senere ‘tidspunkt’). </t>
-  </si>
-  <si>
-    <t>Light can also boost alertness and cognitive function under some conditions.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lys kan også under visse betingelser øge vågenhed og kognitive funktioner.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>In certain situations, light can improve alertness and ability to think.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Under visse omstændigheder kan høje belysningsstyrker øge årvågenhed/ vågenhed og forbedre kognition både i dagtimerne og om natten.  </t>
-  </si>
-  <si>
-    <t>Under some conditions, exposure to high-intensity light during the day and night enhances alertness and improves cognitive performance.</t>
-  </si>
-  <si>
-    <t>What determines these physiological responses to light is primarily determined by how much light reaches the retina and stimulates the ipRGCs at a certain time.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Disse fysiologiske funktioner drevet af lys bestemmes primært af, på et givent tidspunkt, hvor meget lys der når frem til nethinden, og hvor meget de stimulerer de intrinsisk-lysfølsomme retinale ganglieceller (ipRGC’er).  </t>
-    </r>
-  </si>
-  <si>
-    <t>The body's response to light depends on how much light and what time the light reaches the ipRGCs in the retina.</t>
-  </si>
-  <si>
-    <t>Kroppens reaktion på lys afhænger af, hvor meget lys der når ipRGC’erne i øjets nethinde, og på hvilket tidspunkt det sker.  </t>
-  </si>
-  <si>
-    <t>The response of ipRGCs likely depends on the time of day and circadian factors.</t>
-  </si>
-  <si>
-    <t>Higher light levels in the evening can increase the time to fall asleep.</t>
-  </si>
-  <si>
-    <r>
-      <t>Højere belysningslysniveauer om aftenen kan forlænge den tid, det tager at falde i søvn. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Evening light exposure can make it harder to fall asleep.</t>
-  </si>
-  <si>
-    <t>Udsættes man for lys om aftenen, kan det være sværere at falde i søvn.  </t>
-  </si>
-  <si>
-    <t>Evening light exposure tells the body it is still daytime. This increases alertness and shifts the internal clock to a later time.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lys om aftenen fortæller kroppen, at det stadig er dag. Herved øges vågenhed, samt forskydning af det indre ur til et senere ‘tidspunkt’.  </t>
-  </si>
-  <si>
-    <t>Higher light levels during the daytime can improve mood.</t>
-  </si>
-  <si>
-    <r>
-      <t>Højere belysningsniveauer i dagtimerne kan forbedre humøret. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Bright light during the day can improve mood.</t>
-  </si>
-  <si>
-    <t>En højere belysningsstyrke i dagtimerne kan forbedre humøret.  </t>
-  </si>
-  <si>
-    <t>Exposure to natural daylight (the sun) or high-intensity electric light, when free from glare, can reduce stress and improve emotional balance.</t>
-  </si>
-  <si>
-    <t>Eksponering for naturligt dagslys (solen) eller elektrisk belysning med høj intensitet kan, når det er blændfrit, medvirke til at reducere stress og forbedre den ‘følelsesmæssige balance’.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Higher light levels during the daytime can improve sleep quality in the following night. </t>
-  </si>
-  <si>
-    <r>
-      <t>Højere belysningsniveauer i dagtimerne kan forbedre søvnkvaliteten den efterfølgende nat. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Exposure to more intense light during the day can improve sleep.</t>
-  </si>
-  <si>
-    <t>Udsættelse for intenst lys i dagtimerne kan forbedre søvn.  </t>
-  </si>
-  <si>
-    <t>Exposure to higher daytime light levels reduces sleep fragmentation (awakening throughout the night) and increases deep sleep at night.</t>
-  </si>
-  <si>
-    <t>Udsættelse for højere belysningsniveauer i dagtimerne reducerer søvnfragmentering (opvågninger i løbet af natten) og øger mængden af dyb søvn om natten.  </t>
-  </si>
-  <si>
-    <t>Following a medically-prescribed protocol for bright light, exposure in the morning can lead to improvements in mood for people with certain clinical diagnoses.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Ved at følge en medicinsk-/ Lægeordineret protokol for lysterapi kan lyseksponering om morgenen føre til forbedringer i humør hos personer med visse kliniske diagnoser. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Semi-Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Doctors may prescribe light therapy as treatment for winter depression and other health conditions.</t>
-  </si>
-  <si>
-    <t>Læger kan vælge at ordinere lysterapi som behandling for vinterdepression og andre helbredstilstande.  </t>
-  </si>
-  <si>
-    <t>Exposure to bright light has been shown to improve depressive symptoms in individuals with Seasonal Affective Disorder.</t>
-  </si>
-  <si>
-    <t>Eksponering for øgede belysningsstyrker gennem lysterapi har vist sig at forbedre depressive symptomer hos personer med vinterdepression (Seasonal Affective Disorder).  </t>
-  </si>
-  <si>
-    <t>Influencing factors to the non-visual effects of light (21-23)</t>
-  </si>
-  <si>
-    <r>
-      <t>Faktorer med indvirkning på lysets ikke-billeddannede påvirkninger (21–23). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1A62FF"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>A healthy pattern of daily light exposure includes a rhythm of bright light and darkness every day.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>En sund rutine for daglig lyseksponering, skaber en rytme, der både indeholder perioder med øgede belysningsstyrker og perioder med mørke henover døgnet. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>A healthy daily routine includes bright light during the day and darkness at night.</t>
-  </si>
-  <si>
-    <t>En sund daglig rutine indebærer øgede belysningsstyrker i dagtimerne og mørke om natten.  </t>
-  </si>
-  <si>
-    <t>Maintaining a regular pattern of bright light during the day and darkness at night is associated with better physical and mental health.</t>
-  </si>
-  <si>
-    <t>At opretholde et regelmæssigt mønster med øgede belysningsstyrker i dagtimerne og mørke om natten er forbundet med bedre fysisk og mental sundhed.  </t>
-  </si>
-  <si>
-    <t>Age can influence the physiological effect of light on humans, as less light reaches the retina because of ageing.</t>
-  </si>
-  <si>
-    <r>
-      <t>Alder kan påvirke lysets fysiologiske effekt på mennesker, da mindre lys med alderen når øjets nethinde. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>As people age, the lenses of the eye can become less transparent, which may reduce the effects of light on the internal clock and sleep.</t>
-  </si>
-  <si>
-    <t>Med alderen kan øjets linser blive mindre gennemsigtig og klar. Dette kan nedsætte lysets understøttende virkning på det indre ur og søvnen.  </t>
-  </si>
-  <si>
-    <t>With age, the eye’s lenses become less transparent, which may reduce the body’s response to light exposure.</t>
-  </si>
-  <si>
-    <t>Med alderen bliver øjets linse mindre transparent, hvilket kan reducere kroppens respons på en given lyseksponering.  </t>
-  </si>
-  <si>
-    <t>There are substantial individual differences in the physiological response to light.</t>
-  </si>
-  <si>
-    <r>
-      <t>Der findes betydelige individuelle forskelle i hvordan lyset påvirker os.   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>How people respond to light can vary greatly.</t>
-  </si>
-  <si>
-    <t>Hvordan mennesker påvirkes af lys kan variere meget.  </t>
-  </si>
-  <si>
-    <t>Individual differences in light sensitivity are influenced by factors such as age, genetics, and behavior.</t>
-  </si>
-  <si>
-    <t>De Individuelle forskelle i lysfølsomhed influeres af faktorer som alder, genetik og adfærd.  </t>
-  </si>
-  <si>
-    <t>Research in the non-visual effects of light (24-26)</t>
-  </si>
-  <si>
-    <r>
-      <t>Forskning i lysets ikke-billeddannende påvirkninger (24–26). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1A62FF"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>The majority of studies on the physiological effects of light have been performed in the laboratory.</t>
-  </si>
-  <si>
-    <r>
-      <t>Størstedelen af de studier som har set på lysets fysiologiske påvirkning er blevet udført i laboratorier. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Most research on light’s effects on the body has been conducted in the laboratory.</t>
-  </si>
-  <si>
-    <t>Størstedelen af forskningen i lysets indvirkning på kroppen er udført i laboratorier.  </t>
-  </si>
-  <si>
-    <t>Studies investigating light exposure in the real-world are needed.</t>
-  </si>
-  <si>
-    <t>Der er derfor behov for flere studier, der undersøger lyseksponering i virkelige omgivelser i den virkelige verden.  </t>
+    <t>Scientists continue to explore how light affects bodily functions and overall health.</t>
+  </si>
+  <si>
+    <t>Forskere undersøger og afdækker aktivt, hvordan lys påvirker vores krop og vores generelle sundhed.  </t>
+  </si>
+  <si>
+    <t>Scientific and popular interest in the effects of light on biological rhythms, sleep, alertness, mood, and health is growing. Technological and scientific advances are enabling researchers to more precisely study different wavelengths and different intensities.</t>
+  </si>
+  <si>
+    <t>Den videnskabelige og folkelige interesse for lysets indvirkning på biologiske rytmer, søvn, årvågenhed, humør og sundhed er stigende. Denne udbredelse understøttes af teknologiske og videnskabelige fremskridt der nu gør det muligt for forskere mere præcist at kunne undersøge forskellige bølgelængder og forskellige belysningsstyrker i relation til lysets indvirkning på os.  </t>
   </si>
   <si>
     <r>
@@ -941,66 +1010,23 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Forskning i lysets ikke-billeddannende påvirkninger (24–26). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1A62FF"/>
-        <rFont val="Poppins Bold"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>There is a need for studies on the physiological effects of light incorporating a broad range of study populations.</t>
-  </si>
-  <si>
-    <t>Der er behov for studier af lysets fysiologiske påvirkninger, som inddrager et bredere udvalg af studiepopulationer.  </t>
-  </si>
-  <si>
-    <t>More studies are needed to understand how light influences health in different groups of people.</t>
-  </si>
-  <si>
-    <t>Der er behov for flere studier for at få en bedre forståelse af, hvordan lys påvirker sundheden i forskellige populationer.  </t>
-  </si>
-  <si>
-    <t>Most studies on the physiological effects of light have focused on limited populations (specific age groups, ethnicities, or health conditions). It is important that future research studies more diverse populations over wider geographical regions.</t>
-  </si>
-  <si>
-    <t>De fleste studier af lysets fysiologiske påvirkninger har fokuseret på begrænsede populationer (bestemte aldersgrupper, etniciteter eller helbredstilstande). Det er derfor vigtigt, at fremtidig forskning i større grad søger at undersøge mere mangfoldige populationer på tværs af bredere geografiske områder.  </t>
-  </si>
-  <si>
-    <t>The physiological effects of light are an area of active investigation.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lysets fysiologiske påvirkning er et forskningsområde under aktiv udforskning og udvikling. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Scientists continue to explore how light affects bodily functions and overall health.</t>
-  </si>
-  <si>
-    <t>Forskere undersøger og afdækker aktivt, hvordan lys påvirker vores krop og vores generelle sundhed.  </t>
-  </si>
-  <si>
-    <t>Scientific and popular interest in the effects of light on biological rhythms, sleep, alertness, mood, and health is growing. Technological and scientific advances are enabling researchers to more precisely study different wavelengths and different intensities.</t>
-  </si>
-  <si>
-    <t>Den videnskabelige og folkelige interesse for lysets indvirkning på biologiske rytmer, søvn, årvågenhed, humør og sundhed er stigende. Denne udbredelse understøttes af teknologiske og videnskabelige fremskridt der nu gør det muligt for forskere mere præcist at kunne undersøge forskellige bølgelængder og forskellige belysningsstyrker i relation til lysets indvirkning på os.  </t>
+      <t xml:space="preserve">Please note that the References Headline should be changed to - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Referencer</t>
+    </r>
+  </si>
+  <si>
+    <t>A question in regard to; When we see different colours, we are actually seeing different wavelengths of light. Short wavelengths appear violet, while longer wavelengths appear indigo, blue, green, yellow, orange, and red. Would't we in the general public describe BLUE as Shorter wavelength light?????</t>
   </si>
   <si>
     <t>English</t>
@@ -1027,23 +1053,20 @@
     <t>Low light levels in the evening, and darkness while sleeping are part of a healthy light-dark rhythm.</t>
   </si>
   <si>
-    <t>Lave lysniveauer om aftenen og mørke under søvn er en del af et sundt lys-mørke-mønster.</t>
+    <t>Lave lysniveauer om aftenen og mørke under søvn er en del af et sundt lys- og mørkemønster.</t>
   </si>
   <si>
     <t>Managing light exposure is part of a healthy lifestyle, just like diet, exercise, and sleep hygiene.</t>
   </si>
   <si>
     <t>At koordinere og håndtere sin lysudsættelse er en del af en sund livsstil – ligesom kost, motion og en god søvnhygiejne er det.</t>
-  </si>
-  <si>
-    <t>jsh@ocutune.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1144,13 +1167,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF343A40"/>
       <name val="Poppins Bold"/>
       <charset val="1"/>
@@ -1200,8 +1216,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,6 +1246,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1380,7 +1415,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1426,15 +1461,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1442,10 +1469,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1467,9 +1499,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1507,7 +1539,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1613,7 +1645,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1755,7 +1787,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1764,14 +1796,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.375" style="2" customWidth="1"/>
     <col min="2" max="3" width="21.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.1640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="2"/>
+    <col min="4" max="4" width="25.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1805,13 +1837,13 @@
       <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1823,11 +1855,11 @@
         <v>13</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="19" t="s">
-        <v>195</v>
+      <c r="D3" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="18"/>
     </row>
@@ -1849,801 +1881,816 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="49.6640625" customWidth="1"/>
-    <col min="2" max="2" width="65.1640625" customWidth="1"/>
+    <col min="1" max="1" width="49.625" customWidth="1"/>
+    <col min="2" max="2" width="65.125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="43.1640625" customWidth="1"/>
+    <col min="4" max="4" width="43.125" customWidth="1"/>
     <col min="5" max="5" width="134.5" customWidth="1"/>
-    <col min="6" max="7" width="42.33203125" customWidth="1"/>
+    <col min="6" max="7" width="42.375" customWidth="1"/>
     <col min="8" max="8" width="58" customWidth="1"/>
     <col min="9" max="9" width="55" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17">
+    <row r="1" spans="1:9" ht="15.75">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="13" customFormat="1" ht="68">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="13" customFormat="1" ht="60">
       <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="20" t="s">
         <v>22</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C2" s="15">
         <v>1</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="60">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>23</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="68">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="15">
         <v>2</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="22" t="s">
         <v>30</v>
       </c>
+      <c r="E3" s="25" t="s">
+        <v>31</v>
+      </c>
       <c r="F3" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="85">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="20" t="s">
         <v>22</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C4" s="15">
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="23" t="s">
         <v>36</v>
       </c>
+      <c r="E4" s="20" t="s">
+        <v>37</v>
+      </c>
       <c r="F4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="25" t="s">
         <v>38</v>
       </c>
+      <c r="G4" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="H4" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="85">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="20" t="s">
         <v>22</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C5" s="7">
         <v>4</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="23" t="s">
         <v>42</v>
       </c>
+      <c r="E5" s="20" t="s">
+        <v>43</v>
+      </c>
       <c r="F5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="25" t="s">
         <v>44</v>
       </c>
+      <c r="G5" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="H5" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="85">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="74.25">
       <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="20" t="s">
         <v>22</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C6" s="7">
         <v>5</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="23" t="s">
         <v>48</v>
       </c>
+      <c r="E6" s="20" t="s">
+        <v>49</v>
+      </c>
       <c r="F6" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="25" t="s">
         <v>50</v>
       </c>
+      <c r="G6" s="21" t="s">
+        <v>51</v>
+      </c>
       <c r="H6" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="68">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="45">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="20" t="s">
         <v>22</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="C7" s="7">
         <v>6</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="23" t="s">
         <v>54</v>
       </c>
+      <c r="E7" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="F7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="25" t="s">
         <v>56</v>
       </c>
+      <c r="G7" s="21" t="s">
+        <v>57</v>
+      </c>
       <c r="H7" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="70">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="69.95">
       <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="20" t="s">
         <v>60</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="C8" s="7">
         <v>7</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="68.099999999999994">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="68">
-      <c r="A9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>60</v>
       </c>
       <c r="C9" s="7">
         <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="23" t="s">
         <v>68</v>
       </c>
+      <c r="E9" s="20" t="s">
+        <v>69</v>
+      </c>
       <c r="F9" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>68</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="34">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="33.950000000000003">
       <c r="A10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="20" t="s">
         <v>60</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>61</v>
       </c>
       <c r="C10" s="7">
         <v>9</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="23" t="s">
         <v>73</v>
       </c>
+      <c r="E10" s="20" t="s">
+        <v>74</v>
+      </c>
       <c r="F10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="25" t="s">
-        <v>73</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="68">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="68.099999999999994">
       <c r="A11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C11" s="7">
         <v>10</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="68.099999999999994">
+      <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>79</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="68">
-      <c r="A12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>78</v>
       </c>
       <c r="C12" s="7">
         <v>11</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="23" t="s">
         <v>86</v>
       </c>
+      <c r="E12" s="20" t="s">
+        <v>87</v>
+      </c>
       <c r="F12" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="25" t="s">
         <v>88</v>
       </c>
+      <c r="G12" s="21" t="s">
+        <v>89</v>
+      </c>
       <c r="H12" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="51">
       <c r="A13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C13" s="7">
         <v>12</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="23" t="s">
         <v>92</v>
       </c>
+      <c r="E13" s="20" t="s">
+        <v>93</v>
+      </c>
       <c r="F13" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="25" t="s">
         <v>94</v>
       </c>
+      <c r="G13" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="H13" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="51">
       <c r="A14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C14" s="7">
         <v>13</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="23" t="s">
         <v>98</v>
       </c>
+      <c r="E14" s="20" t="s">
+        <v>99</v>
+      </c>
       <c r="F14" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" s="25" t="s">
         <v>100</v>
       </c>
+      <c r="G14" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="H14" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="68">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="68.099999999999994">
       <c r="A15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C15" s="7">
         <v>14</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="23" t="s">
         <v>104</v>
       </c>
+      <c r="E15" s="20" t="s">
+        <v>105</v>
+      </c>
       <c r="F15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" s="25" t="s">
         <v>106</v>
       </c>
+      <c r="G15" s="21" t="s">
+        <v>107</v>
+      </c>
       <c r="H15" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="51">
       <c r="A16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C16" s="7">
         <v>15</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="23" t="s">
         <v>110</v>
       </c>
+      <c r="E16" s="20" t="s">
+        <v>111</v>
+      </c>
       <c r="F16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="G16" s="25" t="s">
         <v>112</v>
       </c>
+      <c r="G16" s="21" t="s">
+        <v>113</v>
+      </c>
       <c r="H16" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="68">
+    </row>
+    <row r="17" spans="1:9" ht="68.099999999999994">
       <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C17" s="7">
         <v>16</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="24" t="s">
         <v>115</v>
       </c>
+      <c r="E17" s="20" t="s">
+        <v>116</v>
+      </c>
       <c r="F17" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G17" s="25" t="s">
         <v>117</v>
       </c>
+      <c r="G17" s="21" t="s">
+        <v>118</v>
+      </c>
       <c r="H17" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="21" t="s">
         <v>118</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="51">
       <c r="A18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C18" s="7">
         <v>17</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="24" t="s">
         <v>120</v>
       </c>
+      <c r="E18" s="20" t="s">
+        <v>121</v>
+      </c>
       <c r="F18" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="25" t="s">
         <v>122</v>
       </c>
+      <c r="G18" s="21" t="s">
+        <v>123</v>
+      </c>
       <c r="H18" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="51">
       <c r="A19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C19" s="7">
         <v>18</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="24" t="s">
         <v>126</v>
       </c>
+      <c r="E19" s="20" t="s">
+        <v>127</v>
+      </c>
       <c r="F19" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="25" t="s">
         <v>128</v>
       </c>
+      <c r="G19" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="H19" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="51">
       <c r="A20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C20" s="7">
         <v>19</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E20" s="24" t="s">
         <v>132</v>
       </c>
+      <c r="E20" s="20" t="s">
+        <v>133</v>
+      </c>
       <c r="F20" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="25" t="s">
         <v>134</v>
       </c>
+      <c r="G20" s="21" t="s">
+        <v>135</v>
+      </c>
       <c r="H20" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="68">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="68.099999999999994">
       <c r="A21" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="20" t="s">
         <v>78</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C21" s="7">
         <v>20</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" s="24" t="s">
         <v>138</v>
       </c>
+      <c r="E21" s="20" t="s">
+        <v>139</v>
+      </c>
       <c r="F21" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" s="25" t="s">
         <v>140</v>
       </c>
+      <c r="G21" s="21" t="s">
+        <v>141</v>
+      </c>
       <c r="H21" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="51">
       <c r="A22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="20" t="s">
         <v>144</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="C22" s="7">
         <v>21</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="68.099999999999994">
+      <c r="A23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="19" t="s">
         <v>145</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="21" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="68">
-      <c r="A23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>144</v>
       </c>
       <c r="C23" s="7">
         <v>22</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23" s="24" t="s">
         <v>152</v>
       </c>
+      <c r="E23" s="20" t="s">
+        <v>153</v>
+      </c>
       <c r="F23" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" s="25" t="s">
         <v>154</v>
       </c>
+      <c r="G23" s="21" t="s">
+        <v>155</v>
+      </c>
       <c r="H23" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="34">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="33.950000000000003">
       <c r="A24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" s="20" t="s">
         <v>144</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="C24" s="7">
         <v>23</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" s="24" t="s">
         <v>158</v>
       </c>
+      <c r="E24" s="20" t="s">
+        <v>159</v>
+      </c>
       <c r="F24" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="G24" s="25" t="s">
         <v>160</v>
       </c>
+      <c r="G24" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="H24" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="51">
       <c r="A25" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="20" t="s">
         <v>164</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>165</v>
       </c>
       <c r="C25" s="7">
         <v>24</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E25" s="24" t="s">
         <v>166</v>
       </c>
+      <c r="E25" s="20" t="s">
+        <v>167</v>
+      </c>
       <c r="F25" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G25" s="25" t="s">
         <v>168</v>
       </c>
+      <c r="G25" s="21" t="s">
+        <v>169</v>
+      </c>
       <c r="H25" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="85">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="84.95">
       <c r="A26" t="s">
-        <v>163</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>171</v>
+        <v>164</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>172</v>
       </c>
       <c r="C26" s="7">
         <v>25</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" s="24" t="s">
         <v>173</v>
       </c>
+      <c r="E26" s="20" t="s">
+        <v>174</v>
+      </c>
       <c r="F26" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="G26" s="25" t="s">
         <v>175</v>
       </c>
+      <c r="G26" s="21" t="s">
+        <v>176</v>
+      </c>
       <c r="H26" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="85">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="84.95">
       <c r="A27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B27" s="20" t="s">
         <v>164</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>165</v>
       </c>
       <c r="C27" s="9">
         <v>26</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="E27" s="24" t="s">
         <v>179</v>
       </c>
+      <c r="E27" s="20" t="s">
+        <v>180</v>
+      </c>
       <c r="F27" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G27" s="25" t="s">
         <v>181</v>
       </c>
+      <c r="G27" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="H27" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>183</v>
-      </c>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75">
+      <c r="A29" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="23"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75">
+      <c r="A31" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -2654,58 +2701,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A98B4A3-5095-AF4B-B22C-B7631D8C258B}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21">
+    <row r="1" spans="1:2" ht="19.5">
       <c r="A1" s="17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="115" customHeight="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="114.95" customHeight="1">
       <c r="A2" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="68">
+        <v>188</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="68.099999999999994">
       <c r="A3" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="85">
+        <v>190</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="84.95">
       <c r="A4" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="84">
+        <v>192</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="79.5">
       <c r="A5" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="85">
+        <v>194</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="84.95">
       <c r="A6" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>194</v>
+        <v>196</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/assets/translations/Danish.Denmark.da-DK.xlsx
+++ b/assets/translations/Danish.Denmark.da-DK.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mspitschan/Projects/LadenburgConsensusStatements/assets/translations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24710C37-71DC-4955-BDDD-AC8E30B96406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A09F83C-D366-854E-95CD-237F5820E533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4300" windowWidth="28800" windowHeight="19080" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13440" yWindow="3880" windowWidth="28800" windowHeight="19080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
     <sheet name="Statements" sheetId="1" r:id="rId2"/>
     <sheet name="Key messages" sheetId="4" r:id="rId3"/>
+    <sheet name="Misc" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="208">
   <si>
     <t>Last name</t>
   </si>
@@ -73,9 +74,6 @@
     <t>DTU Electro</t>
   </si>
   <si>
-    <t>https://orcid.org/0000-0002-4202-4655</t>
-  </si>
-  <si>
     <t>Stormly Hansen</t>
   </si>
   <si>
@@ -107,28 +105,6 @@
   </si>
   <si>
     <t>Light and spectrum (1-6)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Lys- og spektrum (1-6) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1A62FF"/>
-        <rFont val="Poppins Bold"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>Light can be described by its spectrum: how much energy there is at each wavelength across the visible spectrum (from approximately 380 to 780 nm).</t>
   </si>
   <si>
     <r>
@@ -139,53 +115,19 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Lys kan beskrives ud fra dets spektrum: hvor meget energi der findes for hver bølgelængde på tværs af det synlige spektrum (fra cirka 380 til 780 nm). </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Open Sans Bold"/>
+      <t>Lys- og spektrum (1-6) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1A62FF"/>
+        <rFont val="Poppins Bold"/>
       </rPr>
       <t> </t>
     </r>
   </si>
   <si>
-    <t>White light is made up of multiple wavelengths, which we perceive as colours.</t>
-  </si>
-  <si>
-    <t>Hvidt lys består af en mange forskellige bølgelængder, som vi opfatter som farver.  </t>
-  </si>
-  <si>
-    <t>When we see different colours, we are actually seeing different wavelengths of light. Short wavelengths appear violet, while longer wavelengths appear indigo, blue, green, yellow, orange, and red.</t>
-  </si>
-  <si>
-    <r>
-      <t>Når vi ser forskellige farver, svarer det til forskellige bølgelængder i lyset. Lysets korte bølgelængder fremstår som violette, mens lysets længere bølgelængder fremstår som indigo, blå, grøn, gul, orange og rød.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF343A40"/>
-        <rFont val="Poppins Bold"/>
-        <charset val="1"/>
-      </rPr>
-      <t> </t>
-    </r>
-  </si>
-  <si>
-    <t>The pattern of one's light exposure across the day and the year can be quite complex, and depends on where one is and what one does.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>Light can be described by its spectrum: how much energy there is at each wavelength across the visible spectrum (from approximately 380 to 780 nm).</t>
   </si>
   <si>
     <r>
@@ -196,6 +138,63 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Lys kan beskrives ud fra dets spektrum: hvor meget energi der findes for hver bølgelængde på tværs af det synlige spektrum (fra cirka 380 til 780 nm). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Open Sans Bold"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>White light is made up of multiple wavelengths, which we perceive as colours.</t>
+  </si>
+  <si>
+    <t>Hvidt lys består af en mange forskellige bølgelængder, som vi opfatter som farver.  </t>
+  </si>
+  <si>
+    <t>When we see different colours, we are actually seeing different wavelengths of light. Short wavelengths appear violet, while longer wavelengths appear indigo, blue, green, yellow, orange, and red.</t>
+  </si>
+  <si>
+    <r>
+      <t>Når vi ser forskellige farver, svarer det til forskellige bølgelængder i lyset. Lysets korte bølgelængder fremstår som violette, mens lysets længere bølgelængder fremstår som indigo, blå, grøn, gul, orange og rød.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF343A40"/>
+        <rFont val="Poppins Bold"/>
+        <charset val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>The pattern of one's light exposure across the day and the year can be quite complex, and depends on where one is and what one does.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Den lys­eksponering som mennesker udsættes for i løbet af døgnet og året kan være ret komplekst og afhænger af, hvor man befinder sig, og hvad man foretager sig. </t>
     </r>
     <r>
@@ -290,9 +289,6 @@
     <t>We can characterise a light source by describing how much power it emits at each wavelength. This power is called intensity. Physicists measure intensity, while biological and psychological scientists study how intensity affects various processes.</t>
   </si>
   <si>
-    <t>Vi kan karakterisere en lyskilde ved at beskrive, hvor meget effekt den udsender ved hver bølgelængde. Denne effekt kaldes intensitet. Fysikere måler intensitet, mens forskere i biologi og fysiologi undersøger, hvordan intensitet påvirker forskellige processer.</t>
-  </si>
-  <si>
     <t>Daylight has what we call a broad spectrum, with a lot of energy across many wavelengths.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -459,9 +455,6 @@
     <t>Cones are specialized cells in the retina. They are named for their shape (how they appear under a microscope). The highest density of cones is in the fovea (in the centre of the retina).</t>
   </si>
   <si>
-    <t>Tappe er specialiserede celler i nethinden. De har fået deres navn efter deres form (som de ser ud under et mikroskop). Den højeste tæthed af tappe findes i fovea (i midten af nethinden).  </t>
-  </si>
-  <si>
     <t>The rods allow us to see rudimentary spatial detail under dim light.</t>
   </si>
   <si>
@@ -1005,30 +998,6 @@
     <t>Den videnskabelige og folkelige interesse for lysets indvirkning på biologiske rytmer, søvn, årvågenhed, humør og sundhed er stigende. Denne udbredelse understøttes af teknologiske og videnskabelige fremskridt der nu gør det muligt for forskere mere præcist at kunne undersøge forskellige bølgelængder og forskellige belysningsstyrker i relation til lysets indvirkning på os.  </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Please note that the References Headline should be changed to - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Referencer</t>
-    </r>
-  </si>
-  <si>
-    <t>A question in regard to; When we see different colours, we are actually seeing different wavelengths of light. Short wavelengths appear violet, while longer wavelengths appear indigo, blue, green, yellow, orange, and red. Would't we in the general public describe BLUE as Shorter wavelength light?????</t>
-  </si>
-  <si>
     <t>English</t>
   </si>
   <si>
@@ -1060,13 +1029,58 @@
   </si>
   <si>
     <t>At koordinere og håndtere sin lysudsættelse er en del af en sund livsstil – ligesom kost, motion og en god søvnhygiejne er det.</t>
+  </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Consensus statements</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>Nøglebudskaber</t>
+  </si>
+  <si>
+    <t>Referencer</t>
+  </si>
+  <si>
+    <t>Consensus statements (Danish)</t>
+  </si>
+  <si>
+    <t>Chapter</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Statement</t>
+  </si>
+  <si>
+    <t>Simplified Statement</t>
+  </si>
+  <si>
+    <t>Contextual Information</t>
+  </si>
+  <si>
+    <t>0000-0002-4202-4655</t>
+  </si>
+  <si>
+    <t>Vi kan karakterisere en lyskilde ved at beskrive, hvor meget effekt den udsender ved hver bølgelængde. Denne effekt kaldes intensitet. Fysikere måler intensitet, mens biologiske og psykologiske forskere undersøger, hvordan intensitet påvirker forskellige processer.</t>
+  </si>
+  <si>
+    <t>Tappe er specialiserede celler i nethinden. De har fået deres navn efter deres form (som den ser ud under et mikroskop). Den højeste tæthed af tappe findes i fovea (i midten af nethinden).  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1220,13 +1234,29 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1256,7 +1286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1299,21 +1329,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -1411,11 +1426,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1425,22 +1441,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
@@ -1451,33 +1461,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{DF64E03A-D82B-3C4E-8EF8-2F4A3632744D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1499,9 +1515,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1539,7 +1555,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1645,7 +1661,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1787,7 +1803,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1796,14 +1812,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" style="2" customWidth="1"/>
     <col min="2" max="3" width="21.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.875" style="2"/>
+    <col min="4" max="4" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1827,50 +1843,50 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" s="14" customFormat="1">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:7" s="12" customFormat="1">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="12" customFormat="1">
+      <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" s="14" customFormat="1">
-      <c r="A3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="16"/>
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="18"/>
-    </row>
-    <row r="4" spans="1:7" s="14" customFormat="1"/>
-    <row r="5" spans="1:7" s="14" customFormat="1">
-      <c r="D5" s="11"/>
+      <c r="F3" s="16"/>
+    </row>
+    <row r="4" spans="1:7" s="12" customFormat="1"/>
+    <row r="5" spans="1:7" s="12" customFormat="1">
+      <c r="D5" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{9223A398-D56B-48EE-BDD4-337C01CC53CD}"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://orcid.org/0000-0002-4202-4655" xr:uid="{9223A398-D56B-48EE-BDD4-337C01CC53CD}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{3AC593AD-7210-4CC8-93FE-104FB791B2F1}"/>
     <hyperlink ref="D3" r:id="rId3" xr:uid="{EC134B36-4C62-457F-AF2E-764835FBF336}"/>
   </hyperlinks>
@@ -1881,816 +1897,894 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.95"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="49.625" customWidth="1"/>
-    <col min="2" max="2" width="65.125" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="43.125" customWidth="1"/>
-    <col min="5" max="5" width="134.5" customWidth="1"/>
-    <col min="6" max="7" width="42.375" customWidth="1"/>
-    <col min="8" max="8" width="58" customWidth="1"/>
-    <col min="9" max="9" width="55" style="12" customWidth="1"/>
+    <col min="1" max="1" width="49.6640625" customWidth="1"/>
+    <col min="2" max="2" width="65.1640625" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" customWidth="1"/>
+    <col min="6" max="6" width="134.5" customWidth="1"/>
+    <col min="7" max="8" width="42.33203125" customWidth="1"/>
+    <col min="9" max="9" width="58" customWidth="1"/>
+    <col min="10" max="10" width="55" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="11" customFormat="1" ht="68">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="13">
+        <v>1</v>
+      </c>
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="85">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="85">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="13">
+        <v>3</v>
+      </c>
+      <c r="D4" s="13">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="85">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="85">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="68">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="70">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="5">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="68">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="34">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="5">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="68">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="68">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="5">
+        <v>11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="51">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="5">
+        <v>12</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="51">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="5">
+        <v>13</v>
+      </c>
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="68">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="5">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="51">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="5">
+        <v>15</v>
+      </c>
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="68">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="5">
         <v>16</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="51">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="5">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="51">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5">
         <v>18</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="51">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="5">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="68">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="5">
         <v>20</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="D21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="51">
+      <c r="A22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="5">
         <v>21</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="13" customFormat="1" ht="60">
-      <c r="A2" t="s">
+      <c r="D22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="68">
+      <c r="A23" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="5">
         <v>22</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="D23" s="5">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="34">
+      <c r="A24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="5">
         <v>23</v>
       </c>
-      <c r="C2" s="15">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="D24" s="5">
+        <v>23</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="51">
+      <c r="A25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="5">
         <v>24</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="D25" s="5">
+        <v>24</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="85">
+      <c r="A26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="5">
         <v>25</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="D26" s="5">
+        <v>25</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="86" thickBot="1">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="7">
         <v>26</v>
       </c>
-      <c r="G2" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="60">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="15">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="60">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="15">
-        <v>3</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="60">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="74.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7">
-        <v>5</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="45">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="7">
-        <v>6</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="69.95">
-      <c r="A8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="7">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="68.099999999999994">
-      <c r="A9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="7">
-        <v>8</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="33.950000000000003">
-      <c r="A10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="7">
-        <v>9</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="68.099999999999994">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="7">
-        <v>10</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="68.099999999999994">
-      <c r="A12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="7">
-        <v>11</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="51">
-      <c r="A13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="7">
-        <v>12</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="51">
-      <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="7">
-        <v>13</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="68.099999999999994">
-      <c r="A15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="7">
-        <v>14</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="51">
-      <c r="A16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="7">
-        <v>15</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="68.099999999999994">
-      <c r="A17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="7">
-        <v>16</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="51">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="7">
-        <v>17</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="51">
-      <c r="A19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="7">
-        <v>18</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="51">
-      <c r="A20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="7">
-        <v>19</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="68.099999999999994">
-      <c r="A21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="7">
-        <v>20</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="51">
-      <c r="A22" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" s="7">
-        <v>21</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I22" s="21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="68.099999999999994">
-      <c r="A23" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="7">
-        <v>22</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="33.950000000000003">
-      <c r="A24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="7">
-        <v>23</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="I24" s="21" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="51">
-      <c r="A25" t="s">
-        <v>164</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C25" s="7">
-        <v>24</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="84.95">
-      <c r="A26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="7">
-        <v>25</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G26" s="21" t="s">
+      <c r="D27" s="7">
+        <v>26</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="F27" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="I26" s="21" t="s">
+      <c r="G27" s="8" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="84.95">
-      <c r="A27" t="s">
-        <v>164</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C27" s="9">
-        <v>26</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="H27" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="I27" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="J27" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75">
-      <c r="A29" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B29" s="23"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.75">
-      <c r="A31" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="22"/>
+      <c r="B29" s="21"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -2700,59 +2794,106 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A98B4A3-5095-AF4B-B22C-B7631D8C258B}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:2" ht="21">
+      <c r="A1" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="21">
+      <c r="A2" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="115" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="68">
+      <c r="A4" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="85">
+      <c r="A5" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="114.95" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="B5" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="22" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="84">
+      <c r="A6" s="15" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="68.099999999999994">
-      <c r="A3" s="17" t="s">
+      <c r="B6" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="22" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="85">
+      <c r="A7" s="15" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="84.95">
-      <c r="A4" s="17" t="s">
+      <c r="B7" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="22" t="s">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAF359D-FFA8-4D45-B2E3-0F6932B61860}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="24" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="24" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="24" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="79.5">
-      <c r="A5" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="84.95">
-      <c r="A6" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>197</v>
+      <c r="B3" s="25" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
